--- a/Substrates Master.xlsx
+++ b/Substrates Master.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\ProPackHub\apps\estimation-studio\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{435CEA14-13AE-4898-8F7C-8B9229FE4C93}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB9C27B7-775F-427F-AF5A-E2452AB7CBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{6615B560-C438-4DD7-A768-84B0510674C9}"/>
+    <workbookView xWindow="3120" yWindow="3120" windowWidth="21600" windowHeight="11295" xr2:uid="{6615B560-C438-4DD7-A768-84B0510674C9}"/>
   </bookViews>
   <sheets>
     <sheet name="Substrate Costing Master" sheetId="1" r:id="rId1"/>
@@ -490,7 +490,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -512,8 +512,6 @@
     <xf numFmtId="2" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="3" fillId="0" borderId="9" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="5" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -762,13 +760,6 @@
     </dxf>
     <dxf>
       <border outline="0">
-        <bottom style="thin">
-          <color rgb="FFD9D9D9"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <border outline="0">
         <left style="thin">
           <color rgb="FFD9D9D9"/>
         </left>
@@ -806,6 +797,13 @@
           <bgColor indexed="65"/>
         </patternFill>
       </fill>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color rgb="FFD9D9D9"/>
+        </bottom>
+      </border>
     </dxf>
     <dxf>
       <font>
@@ -870,6 +868,7 @@
       <sheetName val="Sleeve"/>
       <sheetName val="Pouch"/>
       <sheetName val="Overall"/>
+      <sheetName val="Costing_form ES"/>
     </sheetNames>
     <sheetDataSet>
       <sheetData sheetId="0"/>
@@ -901,13 +900,14 @@
       </sheetData>
       <sheetData sheetId="6"/>
       <sheetData sheetId="7"/>
+      <sheetData sheetId="8" refreshError="1"/>
     </sheetDataSet>
   </externalBook>
 </externalLink>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2061C019-DE5F-464E-B4B8-8AF64B449090}" name="Table11" displayName="Table11" ref="A1:F47" totalsRowShown="0" headerRowDxfId="10" dataDxfId="9" headerRowBorderDxfId="7" tableBorderDxfId="8" totalsRowBorderDxfId="6" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{2061C019-DE5F-464E-B4B8-8AF64B449090}" name="Table11" displayName="Table11" ref="A1:F47" totalsRowShown="0" headerRowDxfId="10" dataDxfId="8" headerRowBorderDxfId="9" tableBorderDxfId="7" totalsRowBorderDxfId="6" headerRowCellStyle="Normal 2" dataCellStyle="Normal 2">
   <tableColumns count="6">
     <tableColumn id="1" xr3:uid="{EEBA6608-C062-4BC4-868B-B931B893756E}" name="Substrate Family" dataDxfId="5" dataCellStyle="Normal 2"/>
     <tableColumn id="2" xr3:uid="{8D4E1531-7168-4307-BCBD-5D98E2CF92A0}" name="Substrate Grade" dataDxfId="4" dataCellStyle="Normal 2"/>
@@ -1238,18 +1238,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{58FF5465-9BC0-4E3A-B98F-FB70F5D3ED7F}">
   <dimension ref="A1:F47"/>
-  <sheetFormatPr defaultColWidth="8.6640625" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.7109375" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.5546875" style="4" customWidth="1"/>
-    <col min="2" max="2" width="28.77734375" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.5546875" style="4" customWidth="1"/>
+    <col min="1" max="1" width="17.5703125" style="4" customWidth="1"/>
+    <col min="2" max="2" width="28.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.5703125" style="4" customWidth="1"/>
     <col min="4" max="4" width="30" style="4" customWidth="1"/>
     <col min="5" max="5" width="12" style="4" customWidth="1"/>
-    <col min="6" max="6" width="16.44140625" style="4" customWidth="1"/>
-    <col min="7" max="16384" width="8.6640625" style="4"/>
+    <col min="6" max="6" width="16.42578125" style="4" customWidth="1"/>
+    <col min="7" max="16384" width="8.7109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1269,7 +1269,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="5" t="s">
         <v>6</v>
       </c>
@@ -1284,11 +1284,11 @@
         <v>BOPP Transparent</v>
       </c>
       <c r="E2" s="8">
-        <v>2.2000000000000002</v>
+        <v>3</v>
       </c>
       <c r="F2" s="9"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="5" t="s">
         <v>6</v>
       </c>
@@ -1306,7 +1306,7 @@
       </c>
       <c r="F3" s="9"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="5" t="s">
         <v>6</v>
       </c>
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F4" s="9"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="5" t="s">
         <v>6</v>
       </c>
@@ -1342,7 +1342,7 @@
       </c>
       <c r="F5" s="9"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
         <v>6</v>
       </c>
@@ -1360,7 +1360,7 @@
       </c>
       <c r="F6" s="9"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="5" t="s">
         <v>6</v>
       </c>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="F7" s="9"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="5" t="s">
         <v>6</v>
       </c>
@@ -1396,7 +1396,7 @@
       </c>
       <c r="F8" s="9"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
         <v>6</v>
       </c>
@@ -1414,7 +1414,7 @@
       </c>
       <c r="F9" s="9"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="5" t="s">
         <v>6</v>
       </c>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F10" s="9"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="5" t="s">
         <v>23</v>
       </c>
@@ -1450,7 +1450,7 @@
       </c>
       <c r="F11" s="9"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="s">
         <v>23</v>
       </c>
@@ -1468,7 +1468,7 @@
       </c>
       <c r="F12" s="9"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="s">
         <v>23</v>
       </c>
@@ -1486,7 +1486,7 @@
       </c>
       <c r="F13" s="9"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="s">
         <v>23</v>
       </c>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F14" s="9"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="s">
         <v>23</v>
       </c>
@@ -1522,7 +1522,7 @@
       </c>
       <c r="F15" s="9"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="s">
         <v>23</v>
       </c>
@@ -1540,7 +1540,7 @@
       </c>
       <c r="F16" s="9"/>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="s">
         <v>23</v>
       </c>
@@ -1558,7 +1558,7 @@
       </c>
       <c r="F17" s="9"/>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="s">
         <v>23</v>
       </c>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="F18" s="9"/>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="s">
         <v>23</v>
       </c>
@@ -1589,12 +1589,12 @@
       <c r="D19" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="8">
         <v>2.8</v>
       </c>
-      <c r="F19" s="16"/>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="F19" s="9"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="s">
         <v>36</v>
       </c>
@@ -1612,7 +1612,7 @@
       </c>
       <c r="F20" s="9"/>
     </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="s">
         <v>36</v>
       </c>
@@ -1630,7 +1630,7 @@
       </c>
       <c r="F21" s="9"/>
     </row>
-    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="s">
         <v>36</v>
       </c>
@@ -1648,7 +1648,7 @@
       </c>
       <c r="F22" s="9"/>
     </row>
-    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="s">
         <v>36</v>
       </c>
@@ -1666,7 +1666,7 @@
       </c>
       <c r="F23" s="9"/>
     </row>
-    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="s">
         <v>36</v>
       </c>
@@ -1680,11 +1680,11 @@
         <v>45</v>
       </c>
       <c r="E24" s="8">
-        <v>2.1</v>
+        <v>2.2000000000000002</v>
       </c>
       <c r="F24" s="9"/>
     </row>
-    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="s">
         <v>46</v>
       </c>
@@ -1702,7 +1702,7 @@
       </c>
       <c r="F25" s="9"/>
     </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A26" s="5" t="s">
         <v>46</v>
       </c>
@@ -1720,7 +1720,7 @@
       </c>
       <c r="F26" s="9"/>
     </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A27" s="5" t="s">
         <v>46</v>
       </c>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="F27" s="9"/>
     </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="5" t="s">
         <v>46</v>
       </c>
@@ -1756,7 +1756,7 @@
       </c>
       <c r="F28" s="9"/>
     </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="5" t="s">
         <v>46</v>
       </c>
@@ -1774,7 +1774,7 @@
       </c>
       <c r="F29" s="9"/>
     </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="5" t="s">
         <v>53</v>
       </c>
@@ -1792,7 +1792,7 @@
       </c>
       <c r="F30" s="9"/>
     </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="5" t="s">
         <v>53</v>
       </c>
@@ -1810,7 +1810,7 @@
       </c>
       <c r="F31" s="9"/>
     </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A32" s="5" t="s">
         <v>53</v>
       </c>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="F32" s="9"/>
     </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A33" s="5" t="s">
         <v>58</v>
       </c>
@@ -1846,7 +1846,7 @@
       </c>
       <c r="F33" s="9"/>
     </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A34" s="5" t="s">
         <v>61</v>
       </c>
@@ -1865,7 +1865,7 @@
       </c>
       <c r="F34" s="9"/>
     </row>
-    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A35" s="5" t="s">
         <v>61</v>
       </c>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="F35" s="9"/>
     </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A36" s="5" t="s">
         <v>61</v>
       </c>
@@ -1903,7 +1903,7 @@
       </c>
       <c r="F36" s="9"/>
     </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A37" s="5" t="s">
         <v>61</v>
       </c>
@@ -1922,7 +1922,7 @@
       </c>
       <c r="F37" s="9"/>
     </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A38" s="5" t="s">
         <v>61</v>
       </c>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="F38" s="9"/>
     </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A39" s="5" t="s">
         <v>61</v>
       </c>
@@ -1960,7 +1960,7 @@
       </c>
       <c r="F39" s="9"/>
     </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A40" s="5" t="s">
         <v>61</v>
       </c>
@@ -1979,7 +1979,7 @@
       </c>
       <c r="F40" s="9"/>
     </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A41" s="5" t="s">
         <v>69</v>
       </c>
@@ -1997,7 +1997,7 @@
       </c>
       <c r="F41" s="9"/>
     </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A42" s="5" t="s">
         <v>69</v>
       </c>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F42" s="9"/>
     </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A43" s="5" t="s">
         <v>69</v>
       </c>
@@ -2033,7 +2033,7 @@
       </c>
       <c r="F43" s="9"/>
     </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A44" s="5" t="s">
         <v>69</v>
       </c>
@@ -2051,7 +2051,7 @@
       </c>
       <c r="F44" s="9"/>
     </row>
-    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A45" s="5" t="s">
         <v>77</v>
       </c>
@@ -2069,7 +2069,7 @@
       </c>
       <c r="F45" s="9"/>
     </row>
-    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A46" s="5" t="s">
         <v>77</v>
       </c>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="F46" s="9"/>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A47" s="10" t="s">
         <v>77</v>
       </c>
